--- a/artfynd/A 29360-2026 artfynd.xlsx
+++ b/artfynd/A 29360-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746757</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746724</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29360-2026 artfynd.xlsx
+++ b/artfynd/A 29360-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,132 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118746724</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136320432</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9417</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrgärdet, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594823</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6282600</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320432</t>
         </is>
       </c>
     </row>
@@ -929,6 +1055,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
